--- a/data/trans_orig/IP13_R2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si limitaron su actividad por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97762</t>
+          <t>97606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103392</t>
+          <t>103449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128366</t>
+          <t>127779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135269</t>
+          <t>135314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229059</t>
+          <t>229640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>237882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86243</t>
+          <t>85683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93170</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83635</t>
+          <t>84510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92326</t>
+          <t>92510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173670</t>
+          <t>173144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183872</t>
+          <t>184073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46914</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51466</t>
+          <t>51470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56517</t>
+          <t>57450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62994</t>
+          <t>63039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106329</t>
+          <t>105903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113717</t>
+          <t>113621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>18963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206739</t>
+          <t>206181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215262</t>
+          <t>215367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199793</t>
+          <t>199309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211783</t>
+          <t>211485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>410064</t>
+          <t>410350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>425240</t>
+          <t>425243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105145</t>
+          <t>104692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114518</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148715</t>
+          <t>149296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158867</t>
+          <t>159228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258227</t>
+          <t>258037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272121</t>
+          <t>271391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62046</t>
+          <t>62471</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67884</t>
+          <t>67938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63938</t>
+          <t>63812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71156</t>
+          <t>71121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129267</t>
+          <t>129682</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137964</t>
+          <t>137941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>36416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46747</t>
+          <t>45072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>47974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75887</t>
+          <t>74879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>621973</t>
+          <t>620921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>637902</t>
+          <t>637512</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>701755</t>
+          <t>703430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>722911</t>
+          <t>723282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1329952</t>
+          <t>1330960</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1357164</t>
+          <t>1357865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2866</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6856</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118898</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114003</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121167</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>101596</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97606</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>103449</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>132853</t>
+          <t>99970</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127779</t>
+          <t>96094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135314</t>
+          <t>101734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>234449</t>
+          <t>218869</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229640</t>
+          <t>213433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237882</t>
+          <t>222300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6363</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11562</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4364</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8998</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85035</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79836</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88232</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>90317</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>85683</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93168</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89217</t>
+          <t>92287</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84510</t>
+          <t>87567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92510</t>
+          <t>94946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>179535</t>
+          <t>177322</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173144</t>
+          <t>170155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184073</t>
+          <t>181556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2996</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7528</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1687</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4708</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53945</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49413</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56052</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50174</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47153</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51470</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60949</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>48884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63039</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111123</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105903</t>
+          <t>101042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113621</t>
+          <t>108630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10004</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16232</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6148</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2643</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11829</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>191940</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>185712</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>196466</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>211862</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>206181</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>215367</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>206744</t>
+          <t>172791</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199309</t>
+          <t>167780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211485</t>
+          <t>175980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>418606</t>
+          <t>364732</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>410350</t>
+          <t>357203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>425243</t>
+          <t>370377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6694</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12231</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8865</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4965</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14736</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141549</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136012</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144536</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>110563</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>104692</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>114463</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>155413</t>
+          <t>110432</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149296</t>
+          <t>105196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159228</t>
+          <t>114028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>265976</t>
+          <t>251981</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258037</t>
+          <t>244529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271391</t>
+          <t>257187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2928</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6424</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>64799</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>59998</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67378</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>65967</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>62471</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>67938</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>68582</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63812</t>
+          <t>62763</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71121</t>
+          <t>69345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>134549</t>
+          <t>132050</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129682</t>
+          <t>126774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137941</t>
+          <t>135599</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>32685</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23399</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>43240</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>19825</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36416</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34744</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45072</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>58924</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47974</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74879</t>
+          <t>74030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>656166</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>645611</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>665452</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>630479</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>620921</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>637512</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>713758</t>
+          <t>594618</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703430</t>
+          <t>584899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>723282</t>
+          <t>601351</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1344237</t>
+          <t>1250783</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1330960</t>
+          <t>1235677</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1357865</t>
+          <t>1261440</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
